--- a/Templates/water-quality-analysis/example-template-is.xlsx
+++ b/Templates/water-quality-analysis/example-template-is.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-standard-methods\Templates\water-quality-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE34C63B-3883-4C2B-9219-D97811C65A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DE11C1-AC4C-4183-83E4-4184709BBD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample-DateTime" sheetId="21" state="visible" r:id="rId1"/>
@@ -342,7 +342,6 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -371,6 +370,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -394,9 +399,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -992,34 +994,34 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="16" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2697,19 +2699,19 @@
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3583,18 +3585,18 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" customWidth="1"/>
     <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7765,1116 +7767,1247 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" style="13" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="5" max="5" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0001</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0002</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0003</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0004</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0005</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0006</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0007</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0008</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0009</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0010</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0011</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0012</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0013</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0014</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0015</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0016</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0017</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0018</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0019</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0020</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0021</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0022</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0023</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0024</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0025</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0026</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0027</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0028</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0029</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0030</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0031</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0032</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0033</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0034</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0035</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0036</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0037</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0038</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0039</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0040</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0041</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0042</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0043</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0044</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0045</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0046</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0047</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0048</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="3"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="3"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-    </row>
+      <c r="A54" s="3"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="0" orientation="portrait"/>
+  <pageSetup scale="82" fitToHeight="0" orientation="portrait"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
@@ -8888,7 +9021,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -8901,1267 +9034,1529 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0001</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0002</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0003</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0004</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0005</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0006</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0007</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0008</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0009</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0010</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0011</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0012</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0013</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0014</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0015</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0016</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0017</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0018</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0019</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0020</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0021</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0022</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0023</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0024</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0025</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0026</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0027</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0028</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0029</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0030</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0031</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0032</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0033</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0034</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0035</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0036</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0037</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0038</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0039</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0040</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0041</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0042</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0043</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0044</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0045</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0046</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0047</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0048</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
     </row>
     <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
     </row>
     <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
     </row>
     <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="5"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
     </row>
     <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
     </row>
     <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="5"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
     </row>
     <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="5"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
     </row>
     <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-    </row>
-    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="5"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-    </row>
-    <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="5"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-    </row>
-    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="5"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-    </row>
-    <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="5"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-    </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="5"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-    </row>
-    <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-    </row>
-    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="5"/>
-      <c r="B91" s="13"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-    </row>
-    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="5"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-    </row>
-    <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-    </row>
+      <c r="A76" s="3"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="95" fitToHeight="0" orientation="landscape"/>
+  <pageSetup scale="85" fitToHeight="0" orientation="landscape"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
@@ -10175,1116 +10570,1241 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" style="13" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="18"/>
+      <c r="E1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0001</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0002</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0003</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0004</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0005</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0006</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0007</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0008</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0009</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0010</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0011</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0012</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0013</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0014</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0015</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0016</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0017</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0018</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0019</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0020</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0021</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0022</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0023</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0024</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0025</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0026</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0027</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0028</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0029</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0030</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0031</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0032</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0033</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0034</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0035</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0036</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0037</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0038</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0039</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0040</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0041</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0042</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0043</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0044</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0045</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0046</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>SSEMG_COA_IS_____________</t>
         </is>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>SSEMG_R0047</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>SSEMG_R0048</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>SSEMG_STA_IS_____________</t>
         </is>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="3"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="3"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="3"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="3"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="3"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="3"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-    </row>
+      <c r="A53" s="2"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:5" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="98" fitToHeight="0" orientation="portrait"/>
+  <pageSetup scale="84" fitToHeight="0" orientation="portrait"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
